--- a/important_mails_2026-06-08.xlsx
+++ b/important_mails_2026-06-08.xlsx
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -862,78 +862,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
+          <t>Sun, 7 Jun 2026 13:51:46 +0000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (260520getf)</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 3
-Quantity Successfully Destroyed: 3
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3657435-8840459
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-334253755000365</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 7 Jun 2026 13:51:46 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -953,39 +896,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1005,39 +948,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1054,39 +997,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1106,39 +1049,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1155,39 +1098,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 17:51:49 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1206,39 +1149,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1256,39 +1199,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1308,39 +1251,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1358,39 +1301,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1408,39 +1351,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1456,39 +1399,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1507,39 +1450,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1557,39 +1500,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1607,39 +1550,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1657,39 +1600,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -1724,39 +1667,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1772,39 +1715,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 19:32:37 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 5/2026
  96
@@ -1827,39 +1770,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 08:39:32 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Versand durch Amazon for 5/2026
  96
@@ -1883,39 +1826,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:48:24 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -1942,39 +1885,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:51:17 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 5/2026
  96
@@ -2001,39 +1944,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:47:21 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Creditnota Verkoper for 5/2026
  96
@@ -2053,39 +1996,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:42:19 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 5/2026
  96
@@ -2112,39 +2055,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:15:01 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.de Rechnungskorrektur Verkäufer for 5/2026
  96
@@ -2168,39 +2111,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 06:12:39 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Korygująca Sprzedawcy for 5/2026
  96
@@ -2224,39 +2167,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:57:10 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 5/2026
  96
@@ -2274,39 +2217,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:54:32 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 5/2026
  96
@@ -2330,39 +2273,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 05:42:06 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Fulfillment by Amazon for 5/2026
  96
@@ -2385,39 +2328,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:59 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2432,39 +2375,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:01:19 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -2482,39 +2425,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:36:48 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -2541,39 +2484,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:31:12 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -2600,39 +2543,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:43:20 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -2657,39 +2600,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:38:16 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -2714,39 +2657,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -2773,39 +2716,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:21:01 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -2830,39 +2773,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:10:07 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -2889,39 +2832,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:55:24 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -2940,39 +2883,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:25:16 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -2991,39 +2934,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 09:33:20 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -3047,39 +2990,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:52:40 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026
  96
@@ -3103,39 +3046,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:36:30 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -3162,39 +3105,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:48:36 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -3218,39 +3161,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:24:07 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026
  96
@@ -3275,39 +3218,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:01:50 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026
  96
@@ -3332,39 +3275,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:56:14 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026
  96
@@ -3382,39 +3325,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:28:55 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026
  96
@@ -3441,39 +3384,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:23:44 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026
  96
@@ -3491,39 +3434,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:10:53 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026
  96
@@ -3548,39 +3491,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:02:43 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026
  96
@@ -3607,39 +3550,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:45:31 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026
  96
@@ -3660,39 +3603,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 13:05:07 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -3722,39 +3665,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:43:35 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -3779,39 +3722,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:33:36 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -3838,39 +3781,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:16:55 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -3888,39 +3831,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:15 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -3938,39 +3881,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:08 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -3994,39 +3937,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:58:55 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -4051,39 +3994,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:38:44 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -4110,40 +4053,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -4159,40 +4102,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:10:46 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4208,39 +4151,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:37:38 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -4279,39 +4222,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:31:54 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4327,39 +4270,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:14:06 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4375,39 +4318,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:10:02 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -4423,40 +4366,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:43:42 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -4471,40 +4414,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:42:40 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -4518,39 +4461,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:38:41 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -4564,39 +4507,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:37:16 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -4611,39 +4554,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:35:16 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -4657,39 +4600,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:31:58 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -4704,39 +4647,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:35:34 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -4775,39 +4718,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:29:07 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4823,40 +4766,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:25:02 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4872,39 +4815,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:15:34 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -4918,39 +4861,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:56 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4966,40 +4909,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:34 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5015,39 +4958,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5063,39 +5006,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5110,39 +5053,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 13:54:47 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5157,85 +5100,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>96
- Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
- Hola:
- Vamos a lanzar dos nuevos programas para ayudarte a ahorrar en las tarifas de Logística Multicanal.
- A partir del 25 de junio de 2026, podrás ahorrar un 20 % al utilizar Logística Multicanal para entregar pedidos desde cualquier canal de venta externo a Amazon, como tu propio sitio web, tiendas de redes sociales como TikTok Shop, u otros sitios web como eBay.
- Logística Multicanal puede ayudarte a hacer crecer tu negocio, ya que simplifica tus operaciones y proporciona a tus clientes un servicio de entrega rápido y fiable en paquetes sin marca, los siete días de la semana.
- 1. Incentivos para vendedores nuevos:
- si eres un vendedor nuevo de nuestro plan de ventas Profesional y publicas tu primer ASIN apto para la venta a partir del 25 de junio de 2026, puedes recibir un descuento del 20 % en las tarifas de gestión logística de Logística Multicanal para las 100 primeras unidades enviadas durante 12 meses. Para ello, tienes que enviar productos aptos de Logística de Amazon a nuestra red logística en un plazo de 90 días a partir de la publicación de tu primer ASIN apto para la venta.
- A parti</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:38:11 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -5259,39 +5156,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:47:37 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-18</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -5315,39 +5212,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 07:30:07 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>transparency-queue &lt;transparency-queue@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>成功进行 OPR 评估所需采取的措施</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>尊敬的Transparency(透明计划)客户：
 您好！感谢您在Transparency(透明计划)中注册您的商品。
@@ -5367,39 +5264,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -5453,39 +5350,96 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (260520getf)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 3
+Quantity Successfully Destroyed: 3
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3657435-8840459
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-334253755000365</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -5501,39 +5455,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5558,39 +5512,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5610,39 +5564,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5658,39 +5612,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5710,39 +5664,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5762,39 +5716,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -5810,39 +5764,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -5868,39 +5822,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5916,39 +5870,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5973,39 +5927,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6025,39 +5979,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6077,39 +6031,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6129,39 +6083,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6178,39 +6132,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6230,39 +6184,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6282,39 +6236,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6334,39 +6288,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6382,39 +6336,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6431,39 +6385,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6483,39 +6437,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6535,39 +6489,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6584,39 +6538,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6636,39 +6590,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6688,39 +6642,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6737,39 +6691,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6786,39 +6740,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6838,39 +6792,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -6894,39 +6848,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -6950,39 +6904,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7002,39 +6956,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7054,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7106,39 +7060,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7158,39 +7112,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -7206,39 +7160,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7255,39 +7209,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7307,39 +7261,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -7356,40 +7310,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -7406,40 +7360,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -7460,39 +7414,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7510,39 +7464,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7560,39 +7514,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7610,39 +7564,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7660,39 +7614,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -7722,39 +7676,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7773,40 +7727,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7819,40 +7773,40 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -7869,40 +7823,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7919,40 +7873,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -7969,39 +7923,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8021,40 +7975,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8070,40 +8024,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -8119,39 +8073,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -8170,40 +8124,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8219,40 +8173,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8266,40 +8220,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8313,40 +8267,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -8359,39 +8313,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8411,39 +8365,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -8468,39 +8422,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -8525,40 +8479,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8573,40 +8527,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8620,40 +8574,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8664,6 +8618,52 @@
 Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
 For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
 Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
+ Hola:
+ Vamos a lanzar dos nuevos programas para ayudarte a ahorrar en las tarifas de Logística Multicanal.
+ A partir del 25 de junio de 2026, podrás ahorrar un 20 % al utilizar Logística Multicanal para entregar pedidos desde cualquier canal de venta externo a Amazon, como tu propio sitio web, tiendas de redes sociales como TikTok Shop, u otros sitios web como eBay.
+ Logística Multicanal puede ayudarte a hacer crecer tu negocio, ya que simplifica tus operaciones y proporciona a tus clientes un servicio de entrega rápido y fiable en paquetes sin marca, los siete días de la semana.
+ 1. Incentivos para vendedores nuevos:
+ si eres un vendedor nuevo de nuestro plan de ventas Profesional y publicas tu primer ASIN apto para la venta a partir del 25 de junio de 2026, puedes recibir un descuento del 20 % en las tarifas de gestión logística de Logística Multicanal para las 100 primeras unidades enviadas durante 12 meses. Para ello, tienes que enviar productos aptos de Logística de Amazon a nuestra red logística en un plazo de 90 días a partir de la publicación de tu primer ASIN apto para la venta.
+ A parti</t>
         </is>
       </c>
     </row>
